--- a/artfynd/A 31991-2025 artfynd.xlsx
+++ b/artfynd/A 31991-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103435787</v>
+        <v>103435780</v>
       </c>
       <c r="B2" t="n">
-        <v>56717</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103008</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379848.1881127307</v>
+        <v>379645</v>
       </c>
       <c r="R2" t="n">
-        <v>6240746.521308883</v>
+        <v>6240576</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2022-06-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103435766</v>
+        <v>103435771</v>
       </c>
       <c r="B3" t="n">
-        <v>29897</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>200985</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379773.1026068662</v>
+        <v>379773</v>
       </c>
       <c r="R3" t="n">
-        <v>6240707.55934015</v>
+        <v>6240708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2022-06-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103435780</v>
+        <v>103435784</v>
       </c>
       <c r="B4" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,13 +912,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379645.3407557055</v>
+        <v>379721</v>
       </c>
       <c r="R4" t="n">
-        <v>6240576.26529746</v>
+        <v>6240825</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,19 +945,9 @@
           <t>2022-06-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103435771</v>
+        <v>103435787</v>
       </c>
       <c r="B5" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>103008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,13 +1013,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379773.1026068662</v>
+        <v>379848</v>
       </c>
       <c r="R5" t="n">
-        <v>6240707.55934015</v>
+        <v>6240746</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,19 +1046,9 @@
           <t>2022-06-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-06-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,6 +1076,313 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>103435791</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rössjöholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>379848</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6240746</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>103435766</v>
+      </c>
+      <c r="B7" t="n">
+        <v>30288</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>200985</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blanksvart trämyra</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lasius fuliginosus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Latreille, 1798)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rössjöholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>379773</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6240708</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113925536</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rössjöholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>379647</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6240678</v>
+      </c>
+      <c r="S8" t="n">
+        <v>75</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-01-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-01-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31991-2025 artfynd.xlsx
+++ b/artfynd/A 31991-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103435780</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103435771</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103435784</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103435787</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103435791</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103435766</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,8 +1418,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113925536</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>